--- a/Assets/Data/Dungeon0062.xlsx
+++ b/Assets/Data/Dungeon0062.xlsx
@@ -59,10 +59,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -87,24 +87,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -118,8 +110,15 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -133,6 +132,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -140,8 +154,56 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -156,69 +218,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -233,7 +233,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -245,43 +341,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -293,31 +371,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -329,91 +413,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -427,13 +427,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -453,17 +466,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -492,35 +499,28 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -532,19 +532,19 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -553,124 +553,124 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1749,7 +1749,6 @@
       <c r="I10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J10"/>
       <c r="K10" s="1" t="s">
         <v>8</v>
       </c>
@@ -1807,8 +1806,6 @@
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
-      <c r="I11"/>
-      <c r="J11"/>
       <c r="K11" s="1" t="s">
         <v>8</v>
       </c>
@@ -3817,7 +3814,6 @@
       <c r="I10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J10"/>
       <c r="K10" s="1" t="s">
         <v>8</v>
       </c>
@@ -3875,8 +3871,6 @@
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
-      <c r="I11"/>
-      <c r="J11"/>
       <c r="K11" s="1" t="s">
         <v>8</v>
       </c>

--- a/Assets/Data/Dungeon0062.xlsx
+++ b/Assets/Data/Dungeon0062.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="14">
   <si>
     <t>Id</t>
   </si>
@@ -42,10 +42,13 @@
     <t>InitDir</t>
   </si>
   <si>
+    <t>□</t>
+  </si>
+  <si>
     <t>■</t>
   </si>
   <si>
-    <t>Tr:D2</t>
+    <t>Tr:D3</t>
   </si>
   <si>
     <t>Mv</t>
@@ -53,16 +56,19 @@
   <si>
     <t>Ev</t>
   </si>
+  <si>
+    <t>Tr:D2</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -81,29 +87,21 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -117,8 +115,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -140,6 +153,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -147,15 +168,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -172,14 +201,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -188,22 +217,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -211,14 +225,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -233,7 +239,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -245,169 +407,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -427,26 +433,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -466,15 +457,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -486,15 +468,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -524,6 +497,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -532,145 +538,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1338,31 +1344,31 @@
         <v>8</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>8</v>
@@ -1409,7 +1415,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -1418,10 +1424,10 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>8</v>
@@ -1468,27 +1474,27 @@
         <v>8</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>8</v>
@@ -1532,25 +1538,25 @@
         <v>8</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L7" s="1" t="s">
         <v>8</v>
@@ -1597,25 +1603,25 @@
         <v>8</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>8</v>
@@ -1662,27 +1668,27 @@
         <v>8</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>8</v>
@@ -1732,25 +1738,25 @@
         <v>8</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L10" s="1" t="s">
         <v>8</v>
@@ -1796,18 +1802,18 @@
         <v>8</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="K11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L11" s="1" t="s">
         <v>8</v>
@@ -1853,28 +1859,28 @@
         <v>8</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>8</v>
@@ -3255,43 +3261,43 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
@@ -3326,43 +3332,43 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
@@ -3397,43 +3403,43 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
@@ -3468,13 +3474,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -3483,16 +3489,16 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
@@ -3527,39 +3533,39 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
@@ -3594,37 +3600,37 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
@@ -3659,37 +3665,37 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
@@ -3724,39 +3730,39 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
@@ -3791,40 +3797,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
@@ -3855,33 +3861,33 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="K11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
@@ -3912,43 +3918,43 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
@@ -3982,43 +3988,43 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
@@ -4050,43 +4056,43 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>

--- a/Assets/Data/Dungeon0062.xlsx
+++ b/Assets/Data/Dungeon0062.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8410" activeTab="3"/>
+    <workbookView windowWidth="19200" windowHeight="7960" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -96,10 +96,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -117,8 +117,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -132,14 +133,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -148,47 +141,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -201,17 +163,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -225,7 +178,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -240,7 +193,38 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -248,14 +232,30 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -270,7 +270,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -282,7 +282,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -294,7 +336,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -306,31 +372,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -348,13 +426,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -366,91 +438,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -461,6 +461,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -483,22 +498,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -514,15 +514,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -544,11 +535,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -556,8 +545,19 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -569,145 +569,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -5476,8 +5476,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="5"/>
+  <cols>
+    <col min="7" max="7" width="16.7272727272727" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
@@ -5651,23 +5654,23 @@
         <v>62</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D6">
         <v>3010</v>
       </c>
       <c r="F6">
-        <v>1010</v>
+        <v>3020</v>
       </c>
       <c r="G6" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F6,[1]Define!D:D))</f>
-        <v>Adv再生</v>
+        <v>アイテム取得</v>
       </c>
       <c r="H6">
-        <v>110</v>
+        <v>420</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5676,237 +5679,6 @@
         <v>0</v>
       </c>
       <c r="K6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7">
-        <v>62</v>
-      </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-      <c r="D7">
-        <v>3010</v>
-      </c>
-      <c r="F7">
-        <v>7020</v>
-      </c>
-      <c r="G7" t="str">
-        <f>INDEX([1]Define!E:E,MATCH(F7,[1]Define!D:D))</f>
-        <v>怨嗟床</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8">
-        <v>62</v>
-      </c>
-      <c r="B8">
-        <v>3</v>
-      </c>
-      <c r="C8">
-        <v>6</v>
-      </c>
-      <c r="D8">
-        <v>3010</v>
-      </c>
-      <c r="F8">
-        <v>1010</v>
-      </c>
-      <c r="G8" t="str">
-        <f>INDEX([1]Define!E:E,MATCH(F8,[1]Define!D:D))</f>
-        <v>Adv再生</v>
-      </c>
-      <c r="H8">
-        <v>120</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9">
-        <v>62</v>
-      </c>
-      <c r="B9">
-        <v>3</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-      <c r="D9">
-        <v>3010</v>
-      </c>
-      <c r="F9">
-        <v>9010</v>
-      </c>
-      <c r="G9" t="str">
-        <f>INDEX([1]Define!E:E,MATCH(F9,[1]Define!D:D))</f>
-        <v>イベント終了明示</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10">
-        <v>62</v>
-      </c>
-      <c r="B10">
-        <v>4</v>
-      </c>
-      <c r="C10">
-        <v>9</v>
-      </c>
-      <c r="D10">
-        <v>3010</v>
-      </c>
-      <c r="F10">
-        <v>1010</v>
-      </c>
-      <c r="G10" t="str">
-        <f>INDEX([1]Define!E:E,MATCH(F10,[1]Define!D:D))</f>
-        <v>Adv再生</v>
-      </c>
-      <c r="H10">
-        <v>130</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11">
-        <v>62</v>
-      </c>
-      <c r="B11">
-        <v>4</v>
-      </c>
-      <c r="C11">
-        <v>9</v>
-      </c>
-      <c r="D11">
-        <v>3010</v>
-      </c>
-      <c r="F11">
-        <v>7021</v>
-      </c>
-      <c r="G11" t="str">
-        <f>INDEX([1]Define!E:E,MATCH(F11,[1]Define!D:D))</f>
-        <v>怨嗟床解除</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12">
-        <v>62</v>
-      </c>
-      <c r="B12">
-        <v>4</v>
-      </c>
-      <c r="C12">
-        <v>9</v>
-      </c>
-      <c r="D12">
-        <v>3010</v>
-      </c>
-      <c r="F12">
-        <v>9010</v>
-      </c>
-      <c r="G12" t="str">
-        <f>INDEX([1]Define!E:E,MATCH(F12,[1]Define!D:D))</f>
-        <v>イベント終了明示</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13">
-        <v>62</v>
-      </c>
-      <c r="B13">
-        <v>9</v>
-      </c>
-      <c r="C13">
-        <v>4</v>
-      </c>
-      <c r="D13">
-        <v>3010</v>
-      </c>
-      <c r="F13">
-        <v>3020</v>
-      </c>
-      <c r="G13" t="str">
-        <f>INDEX([1]Define!E:E,MATCH(F13,[1]Define!D:D))</f>
-        <v>アイテム取得</v>
-      </c>
-      <c r="H13">
-        <v>420</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13" t="b">
         <v>1</v>
       </c>
     </row>
